--- a/smartshop/EvidenceBasedAdaptiveUI/reports/PersonaOverrides/persona_overrides.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/PersonaOverrides/persona_overrides.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,16 +502,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5667</v>
+        <v>0.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.566667</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.080357</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -530,38 +530,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>mobile_sticky_header</t>
+          <t>desktop_navigation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No (Header scrolls away with content)</t>
+          <t>Mega Menu (Dropdown with images and subcategories)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Yes (Header stays at top while scrolling)</t>
+          <t>Top Bar (Categories always visible across the top)</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5333</v>
+        <v>0.3333</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5333329999999999</v>
+        <v>0.333333</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08</v>
+        <v>0.053571</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest, SHAP</t>
+          <t>Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -572,38 +572,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>urgency_pref</t>
+          <t>desktop_price_display</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>None (I find these annoying and manipulative)</t>
+          <t>Strike-through Original (Shows original price crossed out with sale price)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Both (Show both stock and time based urgency)</t>
+          <t>With Savings Highlighted (Shows discount amount prominently)</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3333</v>
+        <v>0.3056</v>
       </c>
       <c r="G4" t="n">
-        <v>0.333333</v>
+        <v>0.305556</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05</v>
+        <v>0.049107</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest</t>
+          <t>Statistics, Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -614,30 +614,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>desktop_navigation</t>
+          <t>color_theme_pref</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mega Menu (Dropdown with images and subcategories)</t>
+          <t>Vibrant Bold (Bright, energetic colors - exciting and dynamic)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Top Bar (Categories always visible across the top)</t>
+          <t>Minimalist Black &amp; White (Clean, high contrast, professional)</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3333</v>
+        <v>0.2778</v>
       </c>
       <c r="G5" t="n">
-        <v>0.333333</v>
+        <v>0.277778</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05</v>
+        <v>0.044643</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -656,38 +656,38 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>font_style_pref</t>
+          <t>urgency_pref</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1. Modern Sans-serif (Clean, contemporary fonts like Arial or Helvetica)</t>
+          <t>None (I find these annoying and manipulative)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2. Classic Serif (Traditional fonts with decorative strokes like Times New Roman)</t>
+          <t>Both (Show both stock and time based urgency)</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3</v>
+        <v>0.2778</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3</v>
+        <v>0.277778</v>
       </c>
       <c r="H6" t="n">
-        <v>0.045</v>
+        <v>0.044643</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest</t>
+          <t>Statistics, Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -698,30 +698,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>form_field_style</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vibrant Bold (Bright, energetic colors - exciting and dynamic)</t>
+          <t>Outlined (Border around the field)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Minimalist Black &amp; White (Clean, high contrast, professional)</t>
+          <t>Rounded Border Fields (Outlined field with rounded corners)</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3</v>
+        <v>0.2778</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3</v>
+        <v>0.277778</v>
       </c>
       <c r="H7" t="n">
-        <v>0.045</v>
+        <v>0.044643</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -740,30 +740,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_field_style</t>
+          <t>desktop_grid_pref</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Outlined (Border around the field)</t>
+          <t>2 Columns (Large product images, fewer items per row)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Rounded Border Fields (Outlined field with rounded corners)</t>
+          <t>3 Columns (Balanced view, moderate item size)</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3</v>
+        <v>0.2778</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3</v>
+        <v>0.277778</v>
       </c>
       <c r="H8" t="n">
-        <v>0.045</v>
+        <v>0.044643</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -782,38 +782,38 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>font_style_pref</t>
+          <t>desktop_image_text_ratio</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3. Rounded Friendly (Soft, approachable fonts with rounded edges)</t>
+          <t>Balanced (50% images, 50% text - equal emphasis)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2. Classic Serif (Traditional fonts with decorative strokes like Times New Roman)</t>
+          <t>Image-focused (80% images, 20% text - highly visual)</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5</v>
+        <v>0.5312</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.53125</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06</v>
+        <v>0.075893</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest</t>
+          <t>Statistics, Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -824,38 +824,38 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>font_style_pref</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cool Blues (Blues and grays - calm and trustworthy)</t>
+          <t>3. Rounded Friendly (Soft, approachable fonts with rounded edges)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Minimalist Black &amp; White (Clean, high contrast, professional)</t>
+          <t>2. Classic Serif (Traditional fonts with decorative strokes like Times New Roman)</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.333333</v>
+        <v>0.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.04</v>
+        <v>0.07142900000000001</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest, SHAP</t>
+          <t>Statistics, SHAP</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -866,34 +866,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>checkout_style</t>
+          <t>desktop_filter_location</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Progress Bar (Multi step with visual progress indicator)</t>
+          <t>Top Bar (Filters displayed across the top)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>One Page (All checkout steps on a single scrolling page)</t>
+          <t>Sidebar Left (Permanent filter panel on the left side)</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2917</v>
+        <v>0.4375</v>
       </c>
       <c r="G11" t="n">
-        <v>0.291667</v>
+        <v>0.4375</v>
       </c>
       <c r="H11" t="n">
-        <v>0.035</v>
+        <v>0.0625</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest</t>
+          <t>Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -903,133 +903,133 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Impulsive Buyer</t>
+          <t>Deal Hunter</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>desktop_search_visibility</t>
+          <t>desktop_price_display</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Collapsible (Search bar that expands when clicked)</t>
+          <t>With Comparison (Shows similar products' prices)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Always Visible Top (Large, prominent search bar always shown)</t>
+          <t>With Savings Highlighted (Shows discount amount prominently)</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4286</v>
+        <v>0.4062</v>
       </c>
       <c r="G12" t="n">
-        <v>0.428571</v>
+        <v>0.40625</v>
       </c>
       <c r="H12" t="n">
-        <v>0.06</v>
+        <v>0.058036</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Statistics, SHAP</t>
+          <t>Statistics, Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Impulsive Buyer</t>
+          <t>Deal Hunter</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>checkout_style</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Warm Earthy (Browns, beiges, warm oranges - natural and cozy)</t>
+          <t>Progress Bar (Multi step with visual progress indicator)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Minimalist Black &amp; White (Clean, high contrast, professional)</t>
+          <t>One Page (All checkout steps on a single scrolling page)</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>11</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3929</v>
+        <v>0.3438</v>
       </c>
       <c r="G13" t="n">
-        <v>0.392857</v>
+        <v>0.34375</v>
       </c>
       <c r="H13" t="n">
-        <v>0.055</v>
+        <v>0.049107</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest, SHAP</t>
+          <t>Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Impulsive Buyer</t>
+          <t>Deal Hunter</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>checkout_style</t>
+          <t>desktop_grid_pref</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Progress Bar (Multi step with visual progress indicator)</t>
+          <t>4 Columns (Compact view, many items visible at once)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>One Page (All checkout steps on a single scrolling page)</t>
+          <t>3 Columns (Balanced view, moderate item size)</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>11</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3929</v>
+        <v>0.3438</v>
       </c>
       <c r="G14" t="n">
-        <v>0.392857</v>
+        <v>0.34375</v>
       </c>
       <c r="H14" t="n">
-        <v>0.055</v>
+        <v>0.049107</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest</t>
+          <t>Statistics, Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Impulsive Buyer</t>
+          <t>Deal Hunter</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Mega Menu (Dropdown with images and subcategories)</t>
+          <t>Sidebar (Permanent navigation panel on the left)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1048,58 +1048,58 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3214</v>
+        <v>0.3438</v>
       </c>
       <c r="G15" t="n">
-        <v>0.321429</v>
+        <v>0.34375</v>
       </c>
       <c r="H15" t="n">
-        <v>0.045</v>
+        <v>0.049107</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest, SHAP</t>
+          <t>Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Impulsive Buyer</t>
+          <t>Deal Hunter</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>form_field_style</t>
+          <t>color_theme_pref</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Outlined (Border around the field)</t>
+          <t>Cool Blues (Blues and grays - calm and trustworthy)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Rounded Border Fields (Outlined field with rounded corners)</t>
+          <t>Minimalist Black &amp; White (Clean, high contrast, professional)</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2857</v>
+        <v>0.3125</v>
       </c>
       <c r="G16" t="n">
-        <v>0.285714</v>
+        <v>0.3125</v>
       </c>
       <c r="H16" t="n">
-        <v>0.04</v>
+        <v>0.044643</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1118,72 +1118,72 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>product_desc_length</t>
+          <t>checkout_style</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Moderate (Key details with option to expand)</t>
+          <t>Progress Bar (Multi step with visual progress indicator)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Expandable Sections (Organized into collapsible sections)</t>
+          <t>One Page (All checkout steps on a single scrolling page)</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2857</v>
+        <v>0.4</v>
       </c>
       <c r="G17" t="n">
-        <v>0.285714</v>
+        <v>0.4</v>
       </c>
       <c r="H17" t="n">
-        <v>0.04</v>
+        <v>0.053571</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest, SHAP</t>
+          <t>Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Loyal Customer</t>
+          <t>Impulsive Buyer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>desktop_whitespace</t>
+          <t>color_theme_pref</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spacious (clean and uncluttered)</t>
+          <t>Warm Earthy (Browns, beiges, warm oranges - natural and cozy)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Minimalist Black &amp; White (Clean, high contrast, professional)</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5455</v>
+        <v>0.3667</v>
       </c>
       <c r="G18" t="n">
-        <v>0.545455</v>
+        <v>0.366667</v>
       </c>
       <c r="H18" t="n">
-        <v>0.06</v>
+        <v>0.049107</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1197,85 +1197,85 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Loyal Customer</t>
+          <t>Impulsive Buyer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>mobile_review_display</t>
+          <t>desktop_price_display</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Summary Only (Average rating and total count)</t>
+          <t>Bold Large (Price is the most prominent element)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Collapsible Sections (Reviews can be expanded or collapsed within the product details)</t>
+          <t>With Savings Highlighted (Shows discount amount prominently)</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5455</v>
+        <v>0.3333</v>
       </c>
       <c r="G19" t="n">
-        <v>0.545455</v>
+        <v>0.333333</v>
       </c>
       <c r="H19" t="n">
-        <v>0.06</v>
+        <v>0.044643</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Random Forest, SHAP</t>
+          <t>Statistics, Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Loyal Customer</t>
+          <t>Impulsive Buyer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hero_banner_size</t>
+          <t>form_field_style</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Small Strip (Thin banner across the top)</t>
+          <t>Outlined (Border around the field)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Medium Split (Takes up half the screen)</t>
+          <t>Rounded Border Fields (Outlined field with rounded corners)</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5</v>
+        <v>0.2667</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5</v>
+        <v>0.266667</v>
       </c>
       <c r="H20" t="n">
-        <v>0.055</v>
+        <v>0.035714</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Statistics, SHAP</t>
+          <t>Statistics, Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1300,24 +1300,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5</v>
+        <v>0.521739</v>
       </c>
       <c r="H21" t="n">
-        <v>0.055</v>
+        <v>0.053571</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest</t>
+          <t>Statistics, Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1328,34 +1328,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>font_style_pref</t>
+          <t>mobile_product_card</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3. Rounded Friendly (Soft, approachable fonts with rounded edges)</t>
+          <t>Minimal Clean (Simple image, name, price - no clutter)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2. Classic Serif (Traditional fonts with decorative strokes like Times New Roman)</t>
+          <t>Info Rich (Lots of details, ratings, specs visible)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4091</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>0.409091</v>
+        <v>0.521739</v>
       </c>
       <c r="H22" t="n">
-        <v>0.045</v>
+        <v>0.053571</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest</t>
+          <t>Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1370,30 +1370,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>product_desc_length</t>
+          <t>mobile_review_display</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Detailed Full (All specifications and information visible)</t>
+          <t>Summary Only (Average rating and total count)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Expandable Sections (Organized into collapsible sections)</t>
+          <t>Collapsible Sections (Reviews can be expanded or collapsed within the product details)</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3636</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>0.363636</v>
+        <v>0.521739</v>
       </c>
       <c r="H23" t="n">
-        <v>0.04</v>
+        <v>0.053571</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1412,30 +1412,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>background_pref</t>
+          <t>hero_banner_size</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dark (Dark gray or black background)</t>
+          <t>Small Strip (Thin banner across the top)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cream/Off-white (Warm, comfortable, paper-like)</t>
+          <t>Medium Split (Takes up half the screen)</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3182</v>
+        <v>0.4783</v>
       </c>
       <c r="G24" t="n">
-        <v>0.318182</v>
+        <v>0.478261</v>
       </c>
       <c r="H24" t="n">
-        <v>0.035</v>
+        <v>0.049107</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1454,34 +1454,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>urgency_pref</t>
+          <t>desktop_filter_location</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Countdown Timers (Show "Sale ends in 2 hours")</t>
+          <t>Top Bar (Filters displayed across the top)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Both (Show both stock and time based urgency)</t>
+          <t>Sidebar Left (Permanent filter panel on the left side)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3182</v>
+        <v>0.4783</v>
       </c>
       <c r="G25" t="n">
-        <v>0.318182</v>
+        <v>0.478261</v>
       </c>
       <c r="H25" t="n">
-        <v>0.035</v>
+        <v>0.049107</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest</t>
+          <t>Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -1496,76 +1496,76 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>color_theme_pref</t>
+          <t>font_style_pref</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cool Blues (Blues and grays - calm and trustworthy)</t>
+          <t>3. Rounded Friendly (Soft, approachable fonts with rounded edges)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Minimalist Black &amp; White (Clean, high contrast, professional)</t>
+          <t>2. Classic Serif (Traditional fonts with decorative strokes like Times New Roman)</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2727</v>
+        <v>0.3913</v>
       </c>
       <c r="G26" t="n">
-        <v>0.272727</v>
+        <v>0.391304</v>
       </c>
       <c r="H26" t="n">
-        <v>0.03</v>
+        <v>0.040179</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest, SHAP</t>
+          <t>Statistics, SHAP</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Minimalist</t>
+          <t>Loyal Customer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>desktop_image_text_ratio</t>
+          <t>social_proof_display</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Balanced (50% images, 50% text - equal emphasis)</t>
+          <t>Customer Reviews (Written reviews with ratings)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Image-focused (80% images, 20% text - highly visual)</t>
+          <t>User Photos (Photos uploaded by customers)</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4545</v>
+        <v>0.3913</v>
       </c>
       <c r="G27" t="n">
-        <v>0.454545</v>
+        <v>0.391304</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1</v>
+        <v>0.040179</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest</t>
+          <t>Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -1575,77 +1575,77 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Minimalist</t>
+          <t>Loyal Customer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>desktop_search_visibility</t>
+          <t>color_theme_pref</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Collapsible (Search bar that expands when clicked)</t>
+          <t>Warm Earthy (Browns, beiges, warm oranges - natural and cozy)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Always Visible Top (Large, prominent search bar always shown)</t>
+          <t>Minimalist Black &amp; White (Clean, high contrast, professional)</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4545</v>
+        <v>0.3043</v>
       </c>
       <c r="G28" t="n">
-        <v>0.454545</v>
+        <v>0.304348</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1</v>
+        <v>0.03125</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Statistics, SHAP</t>
+          <t>Statistics, Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Researcher</t>
+          <t>Loyal Customer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>desktop_review_display</t>
+          <t>background_pref</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>All Paginated (Show all reviews with pagination)</t>
+          <t>Dark (Dark gray or black background)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Recent 3- 5 (Show a few recent reviews)</t>
+          <t>Cream/Off-white (Warm, comfortable, paper-like)</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4231</v>
+        <v>0.3043</v>
       </c>
       <c r="G29" t="n">
-        <v>0.423077</v>
+        <v>0.304348</v>
       </c>
       <c r="H29" t="n">
-        <v>0.11</v>
+        <v>0.03125</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1659,35 +1659,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Researcher</t>
+          <t>Loyal Customer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>recommendation_type</t>
+          <t>form_field_style</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Category based (Similar items from the same category)</t>
+          <t>Filled Background (Shaded background, no border)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Deals (Products on sale or special offers)</t>
+          <t>Rounded Border Fields (Outlined field with rounded corners)</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3846</v>
+        <v>0.3043</v>
       </c>
       <c r="G30" t="n">
-        <v>0.384615</v>
+        <v>0.304348</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1</v>
+        <v>0.03125</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1701,168 +1701,462 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Researcher</t>
+          <t>Minimalist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>checkout_style</t>
+          <t>desktop_image_text_ratio</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Progress Bar (Multi step with visual progress indicator)</t>
+          <t>Balanced (50% images, 50% text - equal emphasis)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>One Page (All checkout steps on a single scrolling page)</t>
+          <t>Image-focused (80% images, 20% text - highly visual)</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F31" t="n">
-        <v>0.3846</v>
+        <v>0.4898</v>
       </c>
       <c r="G31" t="n">
-        <v>0.384615</v>
+        <v>0.489796</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1</v>
+        <v>0.107143</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest</t>
+          <t>Statistics, Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Researcher</t>
+          <t>Minimalist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>desktop_navigation</t>
+          <t>social_proof_display</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Combination of top bar and dropdowns</t>
+          <t>Customer Reviews (Written reviews with ratings)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Top Bar (Categories always visible across the top)</t>
+          <t>User Photos (Photos uploaded by customers)</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F32" t="n">
-        <v>0.3269</v>
+        <v>0.4694</v>
       </c>
       <c r="G32" t="n">
-        <v>0.326923</v>
+        <v>0.469388</v>
       </c>
       <c r="H32" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.102679</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest, SHAP</t>
+          <t>Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Researcher</t>
+          <t>Minimalist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>form_field_style</t>
+          <t>checkout_style</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Filled Background (Shaded background, no border)</t>
+          <t>Progress Bar (Multi step with visual progress indicator)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Rounded Border Fields (Outlined field with rounded corners)</t>
+          <t>One Page (All checkout steps on a single scrolling page)</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F33" t="n">
-        <v>0.25</v>
+        <v>0.3673</v>
       </c>
       <c r="G33" t="n">
-        <v>0.25</v>
+        <v>0.367347</v>
       </c>
       <c r="H33" t="n">
-        <v>0.065</v>
+        <v>0.080357</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Statistics, Random Forest, SHAP</t>
+          <t>Random Forest, SHAP</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Minimalist</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>mobile_product_card</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Minimal Clean (Simple image, name, price - no clutter)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Info Rich (Lots of details, ratings, specs visible)</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>17</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.346939</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.075893</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Random Forest, SHAP</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Minimalist</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>desktop_product_card</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Minimal Clean (Simple image, name, price - no clutter)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Info Rich (Lots of details, ratings, specs visible)</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>16</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.326531</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.07142900000000001</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Random Forest, SHAP</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>Researcher</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>desktop_review_display</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>All Paginated (Show all reviews with pagination)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Recent 3- 5 (Show a few recent reviews)</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>24</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.444444</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.107143</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Statistics, Random Forest</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>checkout_style</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Progress Bar (Multi step with visual progress indicator)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>One Page (All checkout steps on a single scrolling page)</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>21</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.388889</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Random Forest, SHAP</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>recommendation_type</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Category based (Similar items from the same category)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Deals (Products on sale or special offers)</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>20</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.089286</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Statistics, Random Forest</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>desktop_navigation</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Combination of top bar and dropdowns</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Top Bar (Categories always visible across the top)</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>17</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.314815</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.075893</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Random Forest, SHAP</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>form_field_style</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Filled Background (Shaded background, no border)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Rounded Border Fields (Outlined field with rounded corners)</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>13</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.2407</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.240741</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.058036</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Statistics, Random Forest, SHAP</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
         <is>
           <t>color_theme_pref</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Vibrant Bold (Bright, energetic colors - exciting and dynamic)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Minimalist Black &amp; White (Clean, high contrast, professional)</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E41" t="n">
         <v>12</v>
       </c>
-      <c r="F34" t="n">
-        <v>0.2308</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.230769</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I34" t="inlineStr">
+      <c r="F41" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.222222</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.053571</v>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>Statistics, Random Forest, SHAP</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="J41" t="n">
         <v>3</v>
       </c>
     </row>
